--- a/runac/demo/MPI_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/MPI_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -322,7 +322,7 @@
         <t>Nº DNI
 Qué se espera: texto
 Máximo 15 caracteres.
-Campo obligatorio.</t>
+No es obligatorio.</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
@@ -1211,9 +1211,9 @@
           <t>Situación de documentación</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Nº DNI *</t>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Nº DNI</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -12074,11 +12074,7 @@
           <t>Nº DNI</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
+      <c r="B18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">

--- a/runac/demo/MPI_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
+++ b/runac/demo/MPI_2026_T1_Chubut_CON_ADVERTENCIAS.xlsx
@@ -1469,7 +1469,7 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
-        <v>45625</v>
+        <v>45626</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="BI4" s="5" t="n">
-        <v>45983</v>
+        <v>45984</v>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>45890</v>
+        <v>45891</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="BI5" s="5" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="BI6" s="5" t="n">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="BI7" s="5" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="BI8" s="5" t="n">
-        <v>45850</v>
+        <v>45851</v>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>45874</v>
+        <v>45875</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="R9" s="5" t="n">
-        <v>46336</v>
+        <v>46337</v>
       </c>
       <c r="S9" s="6" t="n">
         <v>90</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="BI9" s="5" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="BI10" s="5" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>45669</v>
+        <v>45670</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="BI11" s="5" t="n">
-        <v>45795</v>
+        <v>45796</v>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="BI12" s="5" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         </is>
       </c>
       <c r="BI13" s="5" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="BI14" s="5" t="n">
-        <v>45616</v>
+        <v>45617</v>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="BI15" s="5" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="BI16" s="5" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="BI17" s="5" t="n">
-        <v>45844</v>
+        <v>45845</v>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="BI18" s="5" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="BI19" s="5" t="n">
-        <v>45822</v>
+        <v>45823</v>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>45714</v>
+        <v>45715</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="BI20" s="5" t="n">
-        <v>45835</v>
+        <v>45836</v>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="BI21" s="5" t="n">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="BI22" s="5" t="n">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="BI23" s="5" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>45712</v>
+        <v>45713</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         </is>
       </c>
       <c r="R24" s="5" t="n">
-        <v>46513</v>
+        <v>46514</v>
       </c>
       <c r="S24" s="6" t="n">
         <v>15</v>
@@ -7857,7 +7857,7 @@
         </is>
       </c>
       <c r="BI24" s="5" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>45947</v>
+        <v>45948</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="BI25" s="5" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="BI26" s="5" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>45585</v>
+        <v>45586</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="BI27" s="5" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="BI28" s="5" t="n">
-        <v>45694</v>
+        <v>45695</v>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>45792</v>
+        <v>45793</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="BI29" s="5" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>45963</v>
+        <v>45964</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="BI30" s="5" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="BI31" s="5" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>45731</v>
+        <v>45732</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         </is>
       </c>
       <c r="BI32" s="5" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="BJ32" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         </is>
       </c>
       <c r="BI33" s="5" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="BJ33" t="inlineStr">
         <is>
